--- a/business_surveys/044_workplace_diversity_perception_survey--business_surveys.xlsx
+++ b/business_surveys/044_workplace_diversity_perception_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -2129,7 +2129,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>action_taken_reason_choices</t>
+          <t>manager_response_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2151,53 +2151,53 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>not_reported</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>manager_response_choices</t>
+          <t>manager_response_reason_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>not_reported</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>manager_response_choices</t>
+          <t>manager_response_reason_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>not_reported</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>manager_response_reason_choices</t>
+          <t>perpetrator_response_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2214,7 +2214,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>manager_response_reason_choices</t>
+          <t>perpetrator_response_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2231,7 +2231,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>manager_response_reason_choices</t>
+          <t>perpetrator_response_reason_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2248,58 +2248,58 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>perpetrator_response_choices</t>
+          <t>perpetrator_response_reason_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>not_reported</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>perpetrator_response_choices</t>
+          <t>bystander_response_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>not_reported</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>perpetrator_response_choices</t>
+          <t>bystander_response_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>not_reported</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not reported</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>perpetrator_response_reason_choices</t>
+          <t>manager_action_taken_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2316,7 +2316,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>perpetrator_response_reason_choices</t>
+          <t>manager_action_taken_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2327,125 +2327,6 @@
       <c r="C72" t="inlineStr">
         <is>
           <t>Not reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>perpetrator_response_reason_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>bystander_response_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>bystander_response_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>not_reported</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>bystander_response_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>manager_action_taken_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>manager_action_taken_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>not_reported</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>manager_action_taken_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
